--- a/00_output/14_programs.xlsx
+++ b/00_output/14_programs.xlsx
@@ -459,8 +459,8 @@
   <dimension ref="A1:D145"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
     <col width="53" customWidth="1" min="4" max="4"/>
   </cols>
@@ -495,7 +495,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -513,7 +513,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -531,7 +531,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -603,7 +603,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -621,7 +621,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -639,7 +639,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -657,7 +657,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -675,7 +675,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -693,7 +693,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -711,7 +711,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -729,7 +729,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -819,7 +819,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -837,7 +837,7 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
@@ -855,7 +855,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -873,7 +873,7 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
@@ -891,7 +891,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -909,7 +909,7 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -945,7 +945,7 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -1035,7 +1035,7 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -1053,7 +1053,7 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
@@ -1071,7 +1071,7 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -1125,7 +1125,7 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
@@ -1143,7 +1143,7 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
@@ -1179,7 +1179,7 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -1251,7 +1251,7 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -1269,7 +1269,7 @@
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
@@ -1287,7 +1287,7 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -1305,7 +1305,7 @@
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -1341,7 +1341,7 @@
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
@@ -1359,7 +1359,7 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -1377,7 +1377,7 @@
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
@@ -1395,7 +1395,7 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -1485,7 +1485,7 @@
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
@@ -1503,7 +1503,7 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -1521,7 +1521,7 @@
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
@@ -1539,7 +1539,7 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -1557,7 +1557,7 @@
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -1593,7 +1593,7 @@
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -1701,7 +1701,7 @@
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
@@ -1719,7 +1719,7 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -1737,7 +1737,7 @@
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -1773,7 +1773,7 @@
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -1809,7 +1809,7 @@
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
@@ -1827,7 +1827,7 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -1899,7 +1899,7 @@
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -1917,7 +1917,7 @@
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
@@ -1935,7 +1935,7 @@
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -1953,7 +1953,7 @@
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
@@ -1971,7 +1971,7 @@
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -1989,7 +1989,7 @@
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
@@ -2007,7 +2007,7 @@
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -2025,7 +2025,7 @@
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
@@ -2043,7 +2043,7 @@
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -2133,7 +2133,7 @@
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="C93" s="4" t="inlineStr">
@@ -2151,7 +2151,7 @@
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -2169,7 +2169,7 @@
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="C95" s="4" t="inlineStr">
@@ -2187,7 +2187,7 @@
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -2205,7 +2205,7 @@
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="C97" s="4" t="inlineStr">
@@ -2223,7 +2223,7 @@
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -2241,7 +2241,7 @@
       </c>
       <c r="B99" s="4" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C99" s="4" t="inlineStr">
@@ -2259,7 +2259,7 @@
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -2331,7 +2331,7 @@
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
@@ -2349,7 +2349,7 @@
       </c>
       <c r="B105" s="4" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="C105" s="4" t="inlineStr">
@@ -2367,7 +2367,7 @@
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
@@ -2385,7 +2385,7 @@
       </c>
       <c r="B107" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="C107" s="4" t="inlineStr">
@@ -2403,7 +2403,7 @@
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="B109" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="C109" s="4" t="inlineStr">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
@@ -2457,7 +2457,7 @@
       </c>
       <c r="B111" s="4" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C111" s="4" t="inlineStr">
@@ -2475,7 +2475,7 @@
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
@@ -2547,7 +2547,7 @@
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B117" s="4" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="C117" s="4" t="inlineStr">
@@ -2583,7 +2583,7 @@
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
@@ -2601,7 +2601,7 @@
       </c>
       <c r="B119" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="C119" s="4" t="inlineStr">
@@ -2619,7 +2619,7 @@
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
@@ -2637,7 +2637,7 @@
       </c>
       <c r="B121" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="C121" s="4" t="inlineStr">
@@ -2655,7 +2655,7 @@
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
@@ -2673,7 +2673,7 @@
       </c>
       <c r="B123" s="4" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C123" s="4" t="inlineStr">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
@@ -2763,7 +2763,7 @@
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
@@ -2781,7 +2781,7 @@
       </c>
       <c r="B129" s="4" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="C129" s="4" t="inlineStr">
@@ -2799,7 +2799,7 @@
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
@@ -2817,7 +2817,7 @@
       </c>
       <c r="B131" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="C131" s="4" t="inlineStr">
@@ -2835,7 +2835,7 @@
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
@@ -2853,7 +2853,7 @@
       </c>
       <c r="B133" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="C133" s="4" t="inlineStr">
@@ -2871,7 +2871,7 @@
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
@@ -2889,7 +2889,7 @@
       </c>
       <c r="B135" s="4" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C135" s="4" t="inlineStr">
@@ -2907,7 +2907,7 @@
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
@@ -2979,7 +2979,7 @@
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr">
@@ -2997,7 +2997,7 @@
       </c>
       <c r="B141" s="4" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="C141" s="4" t="inlineStr">
@@ -3015,7 +3015,7 @@
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="C142" s="2" t="inlineStr">
@@ -3033,7 +3033,7 @@
       </c>
       <c r="B143" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="C143" s="4" t="inlineStr">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="C144" s="2" t="inlineStr">
@@ -3069,7 +3069,7 @@
       </c>
       <c r="B145" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="C145" s="4" t="inlineStr">
